--- a/upload/ШАБЛОН_ИМПОРТА.xlsx
+++ b/upload/ШАБЛОН_ИМПОРТА.xlsx
@@ -31,8 +31,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -44,8 +42,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -70,17 +68,13 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,28 +440,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>№</t>
@@ -495,55 +492,70 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Защита</t>
+          <t>АВР</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>АВР</t>
+          <t>АВР состояние</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>АВР состояние</t>
+          <t>Расположение</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Расположение</t>
+          <t>Шкаф/сборка</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Шкаф/сборка</t>
+          <t>Номинальный ток (А)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Ток (А)</t>
+          <t>Отключ. способность (кА)</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Характеристика</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Ток утечки (мА)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Мощность (кВт)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Длина линии (м)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Кол-во жил</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Сечение (мм²)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Материал</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Допустимый ток (А)</t>
         </is>
@@ -553,58 +565,197 @@
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>ON</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Т1 ТП</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>АВВГ 4х25</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>QF1 ГРЩ1</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>ВА-47-100</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Помещение 1</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n">
+        <v>100</v>
+      </c>
       <c r="K2" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="L2" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="N2" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="O2" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="P2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q2" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>алюминий</t>
         </is>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="S2" s="2" t="n">
         <v>85</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>QF1 ГРЩ1</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>ВВГ 3х16</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>QF2 ЩР1</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Помещение 2</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>ГРЩ1</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>медь</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>QF2 ЩР1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>ВВГ 3х2.5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Нагрузка 1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Помещение 3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>ЩР1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>медь</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -618,200 +769,274 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Марка кабеля</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Количество жил</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Кол-во жил</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Сечение (мм²)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Материал</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Допустимый ток (А)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>R₀ (Ом/км)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>X₀ (Ом/км)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>ВВГ</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="4" t="n">
         <v>2.5</v>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>медь</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="4" t="n">
         <v>7.41</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="4" t="n">
         <v>0.095</v>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>ВВГ</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>медь</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="4" t="n">
         <v>4.61</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="4" t="n">
         <v>0.09</v>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>ВВГ</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>медь</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="4" t="n">
         <v>3.08</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="4" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ВВГ</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>медь</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="H5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>ВВГ</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>медь</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>АВВГ</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C7" s="4" t="n">
         <v>2.5</v>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>алюминий</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E7" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F7" s="4" t="n">
         <v>12.5</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G7" s="4" t="n">
         <v>0.104</v>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="H7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>АВВГ</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>алюминий</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E8" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F8" s="4" t="n">
         <v>7.81</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G8" s="4" t="n">
         <v>0.095</v>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>АВВГ</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>алюминий</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="H9" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -826,63 +1051,56 @@
   </sheetPr>
   <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>описание</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>режим</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>задержка (сек)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>avr1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>АВР ГРЩ1</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Основной АВР</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -899,36 +1117,29 @@
   </sheetPr>
   <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>avr_id</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>элемент</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>роль</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>приоритет</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>сигнал</t>
         </is>
@@ -947,36 +1158,29 @@
   </sheetPr>
   <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>avr_id</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>элемент</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>роль</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>действие_вкл</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>действие_откл</t>
         </is>

--- a/upload/ШАБЛОН_ИМПОРТА.xlsx
+++ b/upload/ШАБЛОН_ИМПОРТА.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -535,27 +535,32 @@
           <t>Мощность (кВт)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Ки</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Длина линии (м)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Кол-во жил</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Сечение (мм²)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Материал</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Допустимый ток (А)</t>
         </is>
@@ -610,21 +615,21 @@
       <c r="N2" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="P2" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q2" s="2" t="n">
+      <c r="R2" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>алюминий</t>
         </is>
       </c>
-      <c r="S2" s="2" t="n">
+      <c r="T2" s="2" t="n">
         <v>85</v>
       </c>
     </row>
@@ -679,21 +684,21 @@
       <c r="N3" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="P3" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="P3" s="2" t="n">
+      <c r="Q3" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q3" s="2" t="n">
+      <c r="R3" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>медь</t>
         </is>
       </c>
-      <c r="S3" s="2" t="n">
+      <c r="T3" s="2" t="n">
         <v>75</v>
       </c>
     </row>
@@ -740,21 +745,21 @@
       <c r="N4" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="P4" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="P4" s="2" t="n">
+      <c r="Q4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q4" s="2" t="n">
+      <c r="R4" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>медь</t>
         </is>
       </c>
-      <c r="S4" s="2" t="n">
+      <c r="T4" s="2" t="n">
         <v>27</v>
       </c>
     </row>

--- a/upload/ШАБЛОН_ИМПОРТА.xlsx
+++ b/upload/ШАБЛОН_ИМПОРТА.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,8 +32,12 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +48,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
         <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -65,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -75,6 +85,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -462,6 +475,9 @@
     <col width="15" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -560,9 +576,19 @@
           <t>Материал</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Допустимый ток (А)</t>
+      <c r="T1" s="5" t="inlineStr">
+        <is>
+          <t>U (кВ)</t>
+        </is>
+      </c>
+      <c r="U1" s="5" t="inlineStr">
+        <is>
+          <t>cos φ</t>
+        </is>
+      </c>
+      <c r="V1" s="5" t="inlineStr">
+        <is>
+          <t>Категория</t>
         </is>
       </c>
     </row>
@@ -629,8 +655,20 @@
           <t>алюминий</t>
         </is>
       </c>
-      <c r="T2" s="2" t="n">
-        <v>85</v>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -698,8 +736,20 @@
           <t>медь</t>
         </is>
       </c>
-      <c r="T3" s="2" t="n">
-        <v>75</v>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -759,9 +809,9 @@
           <t>медь</t>
         </is>
       </c>
-      <c r="T4" s="2" t="n">
-        <v>27</v>
-      </c>
+      <c r="T4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/upload/ШАБЛОН_ИМПОРТА.xlsx
+++ b/upload/ШАБЛОН_ИМПОРТА.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -478,6 +478,7 @@
     <col width="10" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="18" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -591,6 +592,11 @@
           <t>Категория</t>
         </is>
       </c>
+      <c r="W1" s="5" t="inlineStr">
+        <is>
+          <t>Допустимый ток (А)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -670,6 +676,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -749,6 +760,11 @@
       <c r="V3" s="2" t="inlineStr">
         <is>
           <t>3</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -812,6 +828,7 @@
       <c r="T4" s="2" t="inlineStr"/>
       <c r="U4" s="2" t="inlineStr"/>
       <c r="V4" s="2" t="inlineStr"/>
+      <c r="W4" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
